--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3694,10 +3694,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120105932</v>
+        <v>134496485</v>
       </c>
       <c r="B27" t="n">
-        <v>57903</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102110</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3779,22 +3779,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3821,44 +3821,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129145276</v>
+        <v>120105932</v>
       </c>
       <c r="B28" t="n">
-        <v>58607</v>
+        <v>57903</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102124</v>
+        <v>102110</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3898,22 +3906,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3933,59 +3941,51 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson, Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123949465</v>
+        <v>129145276</v>
       </c>
       <c r="B29" t="n">
-        <v>57981</v>
+        <v>58607</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102611</v>
+        <v>102124</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Vinterhämpling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Linaria flavirostris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4025,22 +4025,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4060,17 +4060,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Per-Arne Fransson, Hans Boberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119368623</v>
+        <v>123949465</v>
       </c>
       <c r="B30" t="n">
-        <v>57144</v>
+        <v>57981</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102613</v>
+        <v>102611</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4152,22 +4152,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4194,10 +4194,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133262441</v>
+        <v>119368623</v>
       </c>
       <c r="B31" t="n">
-        <v>57165</v>
+        <v>57144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4224,30 +4224,38 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R31" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,22 +4279,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4301,39 +4309,39 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119403883</v>
+        <v>133262441</v>
       </c>
       <c r="B32" t="n">
-        <v>58424</v>
+        <v>57165</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102624</v>
+        <v>102613</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4343,30 +4351,30 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R32" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4390,34 +4398,29 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hördes från vassen ett par ggr.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4425,22 +4428,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120264782</v>
+        <v>119403883</v>
       </c>
       <c r="B33" t="n">
-        <v>57094</v>
+        <v>58424</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4448,16 +4451,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102931</v>
+        <v>102624</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4467,14 +4470,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4514,29 +4517,34 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hördes från vassen ett par ggr.</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4556,27 +4564,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123949382</v>
+        <v>134496577</v>
       </c>
       <c r="B34" t="n">
-        <v>57105</v>
+        <v>58061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102932</v>
+        <v>102626</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4589,11 +4597,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4633,22 +4649,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4675,10 +4691,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133262975</v>
+        <v>120264782</v>
       </c>
       <c r="B35" t="n">
-        <v>57125</v>
+        <v>57094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4686,45 +4702,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102932</v>
+        <v>102931</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R35" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4748,22 +4768,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4778,22 +4798,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119453310</v>
+        <v>123949382</v>
       </c>
       <c r="B36" t="n">
-        <v>57364</v>
+        <v>57105</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4801,21 +4821,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102954</v>
+        <v>102932</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4827,7 +4847,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4867,22 +4887,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4909,10 +4929,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133263133</v>
+        <v>133262975</v>
       </c>
       <c r="B37" t="n">
-        <v>57386</v>
+        <v>57125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4920,26 +4940,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102954</v>
+        <v>102932</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -5024,10 +5044,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133263328</v>
+        <v>119453310</v>
       </c>
       <c r="B38" t="n">
-        <v>57391</v>
+        <v>57364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5035,21 +5055,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102961</v>
+        <v>102954</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5059,21 +5079,25 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R38" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5097,22 +5121,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5127,22 +5151,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123406233</v>
+        <v>133263133</v>
       </c>
       <c r="B39" t="n">
-        <v>57546</v>
+        <v>57386</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5150,16 +5174,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5169,30 +5193,26 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R39" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5216,22 +5236,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5246,22 +5266,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133263093</v>
+        <v>133263328</v>
       </c>
       <c r="B40" t="n">
-        <v>57568</v>
+        <v>57391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5269,26 +5289,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102963</v>
+        <v>102961</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5373,32 +5393,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132443947</v>
+        <v>123406233</v>
       </c>
       <c r="B41" t="n">
-        <v>57557</v>
+        <v>57546</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102964</v>
+        <v>102963</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5450,22 +5470,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5492,64 +5512,56 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119118339</v>
+        <v>133263093</v>
       </c>
       <c r="B42" t="n">
-        <v>57563</v>
+        <v>57568</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102966</v>
+        <v>102963</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R42" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5573,22 +5585,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5603,68 +5615,72 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133263165</v>
+        <v>132443947</v>
       </c>
       <c r="B43" t="n">
-        <v>57585</v>
+        <v>57557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102966</v>
+        <v>102964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R43" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5688,22 +5704,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5718,56 +5734,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123406081</v>
+        <v>119118339</v>
       </c>
       <c r="B44" t="n">
-        <v>57238</v>
+        <v>57563</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102972</v>
+        <v>102966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Turkduva</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Streptopelia decaocto</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Frivaldszky, 1838)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5807,27 +5827,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ensam</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5854,10 +5869,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126624361</v>
+        <v>133263165</v>
       </c>
       <c r="B45" t="n">
-        <v>57774</v>
+        <v>57585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5865,49 +5880,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102976</v>
+        <v>102966</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R45" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5931,22 +5942,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5961,22 +5972,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119368994</v>
+        <v>123406081</v>
       </c>
       <c r="B46" t="n">
-        <v>58209</v>
+        <v>57238</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5984,33 +5995,33 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102980</v>
+        <v>102972</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Turkduva</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Streptopelia decaocto</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Frivaldszky, 1838)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6050,7 +6061,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6060,12 +6071,17 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ensam</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6092,60 +6108,60 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133263038</v>
+        <v>126624361</v>
       </c>
       <c r="B47" t="n">
-        <v>58231</v>
+        <v>57774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102980</v>
+        <v>102976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R47" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6169,22 +6185,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6199,22 +6215,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119030222</v>
+        <v>119368994</v>
       </c>
       <c r="B48" t="n">
-        <v>58541</v>
+        <v>58209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6222,16 +6238,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6241,7 +6257,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -6288,22 +6304,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6330,10 +6346,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133262639</v>
+        <v>133263038</v>
       </c>
       <c r="B49" t="n">
-        <v>58563</v>
+        <v>58231</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6341,16 +6357,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6360,12 +6376,16 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6445,10 +6465,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120181415</v>
+        <v>119030222</v>
       </c>
       <c r="B50" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6456,33 +6476,33 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6522,22 +6542,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6564,60 +6584,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125041276</v>
+        <v>133262639</v>
       </c>
       <c r="B51" t="n">
-        <v>58463</v>
+        <v>58563</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102995</v>
+        <v>102987</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R51" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6641,22 +6657,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6671,39 +6687,39 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133263233</v>
+        <v>120181415</v>
       </c>
       <c r="B52" t="n">
-        <v>58485</v>
+        <v>58497</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102995</v>
+        <v>102990</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6713,26 +6729,30 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R52" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6756,22 +6776,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6786,56 +6806,56 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123949544</v>
+        <v>125041276</v>
       </c>
       <c r="B53" t="n">
-        <v>58393</v>
+        <v>58463</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102999</v>
+        <v>102995</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6875,22 +6895,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6917,60 +6937,56 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120105993</v>
+        <v>133263233</v>
       </c>
       <c r="B54" t="n">
-        <v>58388</v>
+        <v>58485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103001</v>
+        <v>102995</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R54" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6994,22 +7010,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7024,22 +7040,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118967242</v>
+        <v>123949544</v>
       </c>
       <c r="B55" t="n">
-        <v>58179</v>
+        <v>58393</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7047,33 +7063,33 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103006</v>
+        <v>102999</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7113,22 +7129,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7155,10 +7171,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129410071</v>
+        <v>120105993</v>
       </c>
       <c r="B56" t="n">
-        <v>58179</v>
+        <v>58388</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7166,45 +7182,49 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103006</v>
+        <v>103001</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryd, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>453198</v>
+        <v>453205</v>
       </c>
       <c r="R56" t="n">
-        <v>6377053</v>
+        <v>6377057</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7228,22 +7248,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7258,56 +7278,56 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125041320</v>
+        <v>118967242</v>
       </c>
       <c r="B57" t="n">
-        <v>58286</v>
+        <v>58179</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103008</v>
+        <v>103006</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hermann, 1804)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7347,22 +7367,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7389,60 +7409,56 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119369191</v>
+        <v>129410071</v>
       </c>
       <c r="B58" t="n">
-        <v>58327</v>
+        <v>58179</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>103006</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hermann, 1804)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>453205</v>
+        <v>453198</v>
       </c>
       <c r="R58" t="n">
-        <v>6377057</v>
+        <v>6377053</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7466,22 +7482,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7496,22 +7512,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133011150</v>
+        <v>125041320</v>
       </c>
       <c r="B59" t="n">
-        <v>58461</v>
+        <v>58286</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7519,21 +7535,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103018</v>
+        <v>103008</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7585,22 +7601,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7627,27 +7643,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118967260</v>
+        <v>119369191</v>
       </c>
       <c r="B60" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7704,22 +7720,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7746,44 +7762,44 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119369165</v>
+        <v>133011150</v>
       </c>
       <c r="B61" t="n">
-        <v>58114</v>
+        <v>58461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7823,22 +7839,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7865,10 +7881,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133262933</v>
+        <v>118967260</v>
       </c>
       <c r="B62" t="n">
-        <v>58136</v>
+        <v>58112</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7876,49 +7892,49 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R62" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7942,22 +7958,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7972,68 +7988,72 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133262611</v>
+        <v>119369165</v>
       </c>
       <c r="B63" t="n">
-        <v>58104</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103035</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R63" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8057,22 +8077,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8087,72 +8107,72 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123406104</v>
+        <v>133262933</v>
       </c>
       <c r="B64" t="n">
-        <v>58353</v>
+        <v>58136</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103037</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R64" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8176,22 +8196,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8206,22 +8226,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132443990</v>
+        <v>133262611</v>
       </c>
       <c r="B65" t="n">
-        <v>58596</v>
+        <v>58104</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8229,16 +8249,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103041</v>
+        <v>103035</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8248,30 +8268,26 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R65" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8295,22 +8311,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8325,22 +8341,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120060261</v>
+        <v>123406104</v>
       </c>
       <c r="B66" t="n">
-        <v>58602</v>
+        <v>58353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8348,33 +8364,33 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8414,22 +8430,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8456,10 +8472,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119369236</v>
+        <v>132443990</v>
       </c>
       <c r="B67" t="n">
-        <v>58636</v>
+        <v>58596</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8467,33 +8483,33 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103044</v>
+        <v>103041</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8533,22 +8549,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8575,27 +8591,27 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118967313</v>
+        <v>120060261</v>
       </c>
       <c r="B68" t="n">
-        <v>58649</v>
+        <v>58602</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103057</v>
+        <v>103042</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8605,14 +8621,14 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8652,22 +8668,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8694,10 +8710,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133262505</v>
+        <v>119369236</v>
       </c>
       <c r="B69" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8705,16 +8721,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8724,30 +8740,30 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R69" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8771,22 +8787,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8801,56 +8817,56 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132059774</v>
+        <v>118967313</v>
       </c>
       <c r="B70" t="n">
-        <v>57914</v>
+        <v>58649</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103060</v>
+        <v>103057</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -8890,22 +8906,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8932,60 +8948,60 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119403340</v>
+        <v>133262505</v>
       </c>
       <c r="B71" t="n">
-        <v>57738</v>
+        <v>58671</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>205497</v>
+        <v>103057</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R71" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9009,22 +9025,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9039,44 +9055,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123949519</v>
+        <v>132059774</v>
       </c>
       <c r="B72" t="n">
-        <v>57572</v>
+        <v>57914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>205660</v>
+        <v>103060</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Brun glada</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Milvus migrans</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9084,11 +9100,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
@@ -9132,27 +9144,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>med 6 Fiskmåsar</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9179,27 +9186,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118967185</v>
+        <v>119403340</v>
       </c>
       <c r="B73" t="n">
-        <v>58085</v>
+        <v>57738</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>205976</v>
+        <v>205497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Ägretthäger</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ardea alba</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9209,14 +9216,14 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9256,22 +9263,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9298,32 +9305,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>78986241</v>
+        <v>123949519</v>
       </c>
       <c r="B74" t="n">
-        <v>56884</v>
+        <v>57572</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>208255</v>
+        <v>205660</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9331,12 +9338,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9376,22 +9386,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>med 6 Fiskmåsar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9400,7 +9415,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9419,10 +9433,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>86131648</v>
+        <v>118967185</v>
       </c>
       <c r="B75" t="n">
-        <v>45298</v>
+        <v>58085</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9430,54 +9444,49 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>208306</v>
+        <v>205976</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>453186</v>
+        <v>453205</v>
       </c>
       <c r="R75" t="n">
-        <v>6377118</v>
+        <v>6377057</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9501,22 +9510,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9525,22 +9534,267 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>78986241</v>
+      </c>
+      <c r="B76" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>453205</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6377057</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2019-07-19</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2019-07-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>86131648</v>
+      </c>
+      <c r="B77" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>453186</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6377118</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>Bo Andersson</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Bo Andersson</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2238,27 +2238,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99972724</v>
+        <v>135507212</v>
       </c>
       <c r="B15" t="n">
-        <v>56766</v>
+        <v>57366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100077</v>
+        <v>100075</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Myrspov</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Limosa lapponica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2268,14 +2268,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2357,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123405827</v>
+        <v>99972724</v>
       </c>
       <c r="B16" t="n">
-        <v>57049</v>
+        <v>56766</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100079</v>
+        <v>100077</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2434,27 +2434,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 hanar och 1 hona</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,10 +2476,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119030176</v>
+        <v>123405827</v>
       </c>
       <c r="B17" t="n">
-        <v>57890</v>
+        <v>57049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,16 +2487,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100082</v>
+        <v>100079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2511,18 +2506,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2562,27 +2553,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>över Målen</t>
+          <t>2 hanar och 1 hona</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2609,10 +2600,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133263241</v>
+        <v>119030176</v>
       </c>
       <c r="B18" t="n">
-        <v>57912</v>
+        <v>57890</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,26 +2630,34 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R18" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2682,22 +2681,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>över Målen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2712,39 +2716,39 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119813682</v>
+        <v>133263241</v>
       </c>
       <c r="B19" t="n">
-        <v>58067</v>
+        <v>57912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100090</v>
+        <v>100082</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2754,30 +2758,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R19" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2801,22 +2801,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,39 +2831,39 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123949501</v>
+        <v>119813682</v>
       </c>
       <c r="B20" t="n">
-        <v>57340</v>
+        <v>58067</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100091</v>
+        <v>100090</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2873,14 +2873,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2962,27 +2962,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119030171</v>
+        <v>123949501</v>
       </c>
       <c r="B21" t="n">
-        <v>57825</v>
+        <v>57340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100096</v>
+        <v>100091</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2992,14 +2992,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3039,22 +3039,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,10 +3081,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133262669</v>
+        <v>119030171</v>
       </c>
       <c r="B22" t="n">
-        <v>57847</v>
+        <v>57825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3116,21 +3116,25 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R22" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3154,22 +3158,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3184,39 +3188,39 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119118353</v>
+        <v>133262669</v>
       </c>
       <c r="B23" t="n">
-        <v>57838</v>
+        <v>57847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100100</v>
+        <v>100096</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3229,35 +3233,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R23" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3281,22 +3273,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3311,44 +3303,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133128748</v>
+        <v>119118353</v>
       </c>
       <c r="B24" t="n">
-        <v>57291</v>
+        <v>57838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100116</v>
+        <v>100100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Småfläckig sumphöna</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porzana porzana</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3356,11 +3348,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3400,27 +3400,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Två "visslingar" hördes .</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3447,32 +3442,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133094051</v>
+        <v>133128748</v>
       </c>
       <c r="B25" t="n">
-        <v>58225</v>
+        <v>57291</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100124</v>
+        <v>100116</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Småfläckig sumphöna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Porzana porzana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3484,7 +3479,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3524,22 +3519,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Två "visslingar" hördes .</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3566,44 +3566,40 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119403328</v>
+        <v>133094051</v>
       </c>
       <c r="B26" t="n">
-        <v>57505</v>
+        <v>58225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100134</v>
+        <v>100124</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skräntärna</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydroprogne caspia</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
@@ -3647,27 +3643,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>drog nog mot söder efter en stunds födosökande</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3694,37 +3685,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134496485</v>
+        <v>119403328</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>57505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100134</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skräntärna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydroprogne caspia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3732,14 +3723,10 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3779,22 +3766,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>drog nog mot söder efter en stunds födosökande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3821,10 +3813,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120105932</v>
+        <v>134496485</v>
       </c>
       <c r="B28" t="n">
-        <v>57903</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3832,21 +3824,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102110</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3866,7 +3858,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3906,22 +3898,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3948,44 +3940,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129145276</v>
+        <v>120105932</v>
       </c>
       <c r="B29" t="n">
-        <v>58607</v>
+        <v>57903</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102124</v>
+        <v>102110</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4025,22 +4025,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4060,59 +4060,51 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson, Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123949465</v>
+        <v>129145276</v>
       </c>
       <c r="B30" t="n">
-        <v>57981</v>
+        <v>58607</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102611</v>
+        <v>102124</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Vinterhämpling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Linaria flavirostris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4152,22 +4144,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4187,17 +4179,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Per-Arne Fransson, Hans Boberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119368623</v>
+        <v>123949465</v>
       </c>
       <c r="B31" t="n">
-        <v>57144</v>
+        <v>57981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4205,21 +4197,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102613</v>
+        <v>102611</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4239,7 +4231,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4279,22 +4271,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4321,10 +4313,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133262441</v>
+        <v>119368623</v>
       </c>
       <c r="B32" t="n">
-        <v>57165</v>
+        <v>57144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4351,30 +4343,38 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R32" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4398,22 +4398,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4428,39 +4428,39 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119403883</v>
+        <v>133262441</v>
       </c>
       <c r="B33" t="n">
-        <v>58424</v>
+        <v>57165</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102624</v>
+        <v>102613</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4470,30 +4470,30 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R33" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4517,34 +4517,29 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hördes från vassen ett par ggr.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4552,44 +4547,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134496577</v>
+        <v>119403883</v>
       </c>
       <c r="B34" t="n">
-        <v>58061</v>
+        <v>58424</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102626</v>
+        <v>102624</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4597,19 +4592,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4649,29 +4636,34 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hördes från vassen ett par ggr.</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4691,44 +4683,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120264782</v>
+        <v>134496577</v>
       </c>
       <c r="B35" t="n">
-        <v>57094</v>
+        <v>58061</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102931</v>
+        <v>102626</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4768,22 +4768,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4810,10 +4810,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123949382</v>
+        <v>120264782</v>
       </c>
       <c r="B36" t="n">
-        <v>57105</v>
+        <v>57094</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4821,33 +4821,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102932</v>
+        <v>102931</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4887,22 +4887,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133262975</v>
+        <v>123949382</v>
       </c>
       <c r="B37" t="n">
-        <v>57125</v>
+        <v>57105</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4959,26 +4959,30 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R37" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5002,22 +5006,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5032,22 +5036,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119453310</v>
+        <v>133262975</v>
       </c>
       <c r="B38" t="n">
-        <v>57364</v>
+        <v>57125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5055,49 +5059,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102954</v>
+        <v>102932</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R38" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5121,22 +5121,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5151,22 +5151,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133263133</v>
+        <v>119453310</v>
       </c>
       <c r="B39" t="n">
-        <v>57386</v>
+        <v>57364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,21 +5198,25 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R39" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5236,22 +5240,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5266,22 +5270,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133263328</v>
+        <v>133263133</v>
       </c>
       <c r="B40" t="n">
-        <v>57391</v>
+        <v>57386</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5289,21 +5293,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102961</v>
+        <v>102954</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5393,10 +5397,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123406233</v>
+        <v>133263328</v>
       </c>
       <c r="B41" t="n">
-        <v>57546</v>
+        <v>57391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,49 +5408,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102963</v>
+        <v>102961</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R41" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5470,22 +5470,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5500,22 +5500,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133263093</v>
+        <v>123406233</v>
       </c>
       <c r="B42" t="n">
-        <v>57568</v>
+        <v>57546</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5542,26 +5542,30 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R42" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5585,22 +5589,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5615,72 +5619,68 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132443947</v>
+        <v>133263093</v>
       </c>
       <c r="B43" t="n">
-        <v>57557</v>
+        <v>57568</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102964</v>
+        <v>102963</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R43" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5704,22 +5704,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5734,60 +5734,56 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119118339</v>
+        <v>132443947</v>
       </c>
       <c r="B44" t="n">
-        <v>57563</v>
+        <v>57557</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102966</v>
+        <v>102964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5827,22 +5823,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5869,10 +5865,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133263165</v>
+        <v>119118339</v>
       </c>
       <c r="B45" t="n">
-        <v>57585</v>
+        <v>57563</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5899,26 +5895,34 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R45" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5942,22 +5946,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5972,44 +5976,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123406081</v>
+        <v>133263165</v>
       </c>
       <c r="B46" t="n">
-        <v>57238</v>
+        <v>57585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102972</v>
+        <v>102966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Turkduva</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Streptopelia decaocto</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Frivaldszky, 1838)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6019,25 +6023,21 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R46" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6061,27 +6061,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ensam</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6096,56 +6091,56 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126624361</v>
+        <v>123406081</v>
       </c>
       <c r="B47" t="n">
-        <v>57774</v>
+        <v>57238</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102976</v>
+        <v>102972</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Turkduva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Streptopelia decaocto</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Frivaldszky, 1838)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6185,22 +6180,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ensam</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6227,44 +6227,44 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119368994</v>
+        <v>126624361</v>
       </c>
       <c r="B48" t="n">
-        <v>58209</v>
+        <v>57774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102980</v>
+        <v>102976</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6304,22 +6304,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6346,10 +6346,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133263038</v>
+        <v>119368994</v>
       </c>
       <c r="B49" t="n">
-        <v>58231</v>
+        <v>58209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6376,30 +6376,30 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R49" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6423,22 +6423,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6453,22 +6453,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119030222</v>
+        <v>133263038</v>
       </c>
       <c r="B50" t="n">
-        <v>58541</v>
+        <v>58231</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6476,16 +6476,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6495,30 +6495,30 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R50" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6542,22 +6542,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6572,22 +6572,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133262639</v>
+        <v>119030222</v>
       </c>
       <c r="B51" t="n">
-        <v>58563</v>
+        <v>58541</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6614,26 +6614,30 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R51" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6657,22 +6661,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6687,22 +6691,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120181415</v>
+        <v>133262639</v>
       </c>
       <c r="B52" t="n">
-        <v>58497</v>
+        <v>58563</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6710,21 +6714,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6734,25 +6738,21 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R52" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6776,22 +6776,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6806,39 +6806,39 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125041276</v>
+        <v>120181415</v>
       </c>
       <c r="B53" t="n">
-        <v>58463</v>
+        <v>58497</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102995</v>
+        <v>102990</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6848,14 +6848,14 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6895,22 +6895,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6937,10 +6937,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133263233</v>
+        <v>125041276</v>
       </c>
       <c r="B54" t="n">
-        <v>58485</v>
+        <v>58463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6972,21 +6972,25 @@
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R54" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7010,22 +7014,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7040,72 +7044,68 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123949544</v>
+        <v>133263233</v>
       </c>
       <c r="B55" t="n">
-        <v>58393</v>
+        <v>58485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102999</v>
+        <v>102995</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R55" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7129,22 +7129,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7159,22 +7159,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120105993</v>
+        <v>123949544</v>
       </c>
       <c r="B56" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7182,33 +7182,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7248,22 +7248,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7290,10 +7290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118967242</v>
+        <v>120105993</v>
       </c>
       <c r="B57" t="n">
-        <v>58179</v>
+        <v>58388</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7301,33 +7301,33 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103006</v>
+        <v>103001</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7367,22 +7367,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7409,7 +7409,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129410071</v>
+        <v>118967242</v>
       </c>
       <c r="B58" t="n">
         <v>58179</v>
@@ -7437,28 +7437,32 @@
           <t>(Hermann, 1804)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryd, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>453198</v>
+        <v>453205</v>
       </c>
       <c r="R58" t="n">
-        <v>6377053</v>
+        <v>6377057</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7482,22 +7486,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7512,51 +7516,47 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125041320</v>
+        <v>129410071</v>
       </c>
       <c r="B59" t="n">
-        <v>58286</v>
+        <v>58179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103008</v>
+        <v>103006</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hermann, 1804)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
@@ -7567,17 +7567,17 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>453205</v>
+        <v>453198</v>
       </c>
       <c r="R59" t="n">
-        <v>6377057</v>
+        <v>6377053</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7601,22 +7601,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7631,22 +7631,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119369191</v>
+        <v>125041320</v>
       </c>
       <c r="B60" t="n">
-        <v>58327</v>
+        <v>58286</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7654,16 +7654,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7720,22 +7720,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7762,10 +7762,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133011150</v>
+        <v>119369191</v>
       </c>
       <c r="B61" t="n">
-        <v>58461</v>
+        <v>58327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7773,33 +7773,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7839,22 +7839,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7881,44 +7881,44 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118967260</v>
+        <v>133011150</v>
       </c>
       <c r="B62" t="n">
-        <v>58112</v>
+        <v>58461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7958,22 +7958,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8000,10 +8000,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119369165</v>
+        <v>118967260</v>
       </c>
       <c r="B63" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8011,26 +8011,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -8077,22 +8077,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8119,10 +8119,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133262933</v>
+        <v>119369165</v>
       </c>
       <c r="B64" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8149,30 +8149,30 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R64" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8196,22 +8196,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8226,54 +8226,58 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133262611</v>
+        <v>133262933</v>
       </c>
       <c r="B65" t="n">
-        <v>58104</v>
+        <v>58136</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103035</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8353,27 +8357,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123406104</v>
+        <v>133262611</v>
       </c>
       <c r="B66" t="n">
-        <v>58353</v>
+        <v>58104</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8383,30 +8387,26 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R66" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8430,22 +8430,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8460,39 +8460,39 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132443990</v>
+        <v>123406104</v>
       </c>
       <c r="B67" t="n">
-        <v>58596</v>
+        <v>58353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103041</v>
+        <v>103037</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -8549,22 +8549,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8591,44 +8591,44 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120060261</v>
+        <v>132443990</v>
       </c>
       <c r="B68" t="n">
-        <v>58602</v>
+        <v>58596</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8668,22 +8668,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8710,27 +8710,27 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119369236</v>
+        <v>120060261</v>
       </c>
       <c r="B69" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8740,14 +8740,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8787,22 +8787,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8829,10 +8829,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118967313</v>
+        <v>119369236</v>
       </c>
       <c r="B70" t="n">
-        <v>58649</v>
+        <v>58636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8840,16 +8840,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8866,7 +8866,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -8906,22 +8906,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8948,10 +8948,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133262505</v>
+        <v>118967313</v>
       </c>
       <c r="B71" t="n">
-        <v>58671</v>
+        <v>58649</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8978,30 +8978,30 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R71" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9025,22 +9025,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9055,72 +9055,72 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059774</v>
+        <v>133262505</v>
       </c>
       <c r="B72" t="n">
-        <v>57914</v>
+        <v>58671</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103060</v>
+        <v>103057</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R72" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9144,22 +9144,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9174,56 +9174,56 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119403340</v>
+        <v>132059774</v>
       </c>
       <c r="B73" t="n">
-        <v>57738</v>
+        <v>57914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>205497</v>
+        <v>103060</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Brun glada</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Milvus migrans</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9263,17 +9263,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -9305,10 +9305,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123949519</v>
+        <v>119403340</v>
       </c>
       <c r="B74" t="n">
-        <v>57572</v>
+        <v>57738</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9316,16 +9316,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>205660</v>
+        <v>205497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Ägretthäger</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ardea alba</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9335,18 +9335,14 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9386,27 +9382,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>med 6 Fiskmåsar</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9433,27 +9424,27 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118967185</v>
+        <v>123949519</v>
       </c>
       <c r="B75" t="n">
-        <v>58085</v>
+        <v>57572</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>205976</v>
+        <v>205660</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9463,14 +9454,18 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -9510,22 +9505,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>med 6 Fiskmåsar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9552,10 +9552,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>78986241</v>
+        <v>118967185</v>
       </c>
       <c r="B76" t="n">
-        <v>56884</v>
+        <v>58085</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9563,34 +9563,33 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208255</v>
+        <v>205976</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -9630,22 +9629,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9654,7 +9653,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9673,10 +9671,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>86131648</v>
+        <v>78986241</v>
       </c>
       <c r="B77" t="n">
-        <v>45298</v>
+        <v>56884</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9684,21 +9682,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>208306</v>
+        <v>208255</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9707,11 +9705,7 @@
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
@@ -9721,17 +9715,17 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>453186</v>
+        <v>453205</v>
       </c>
       <c r="R77" t="n">
-        <v>6377118</v>
+        <v>6377057</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9755,22 +9749,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9786,15 +9780,140 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>86131648</v>
+      </c>
+      <c r="B78" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>453186</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6377118</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
           <t>Bo Andersson</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AX78" t="inlineStr">
         <is>
           <t>Bo Andersson</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73632095</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813636</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1160,6 +1180,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813778</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1304,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120181295</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1398,6 +1428,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120264778</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,6 +1552,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120241633</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1632,6 +1672,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262981</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1755,6 +1800,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119403475</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1874,6 +1924,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119030185</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1989,6 +2044,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262268</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2112,6 +2172,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967209</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2235,6 +2300,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813551</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2354,6 +2424,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135507212</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2473,6 +2548,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99972724</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2597,6 +2677,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123405827</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2725,6 +2810,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119030176</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2840,6 +2930,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263241</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2959,6 +3054,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813682</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3078,6 +3178,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123949501</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3197,6 +3302,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119030171</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3312,6 +3422,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262669</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3439,13 +3554,18 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119118353</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133128748</v>
+        <v>135560489</v>
       </c>
       <c r="B25" t="n">
-        <v>57291</v>
+        <v>57436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3453,33 +3573,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100116</v>
+        <v>100103</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Småfläckig sumphöna</t>
+          <t>Brushane</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porzana porzana</t>
+          <t>Calidris pugnax</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3519,27 +3643,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Två "visslingar" hördes .</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3563,35 +3682,40 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135560489</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133094051</v>
+        <v>133128748</v>
       </c>
       <c r="B26" t="n">
-        <v>58225</v>
+        <v>57291</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100124</v>
+        <v>100116</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Småfläckig sumphöna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Porzana porzana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3603,7 +3727,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3643,22 +3767,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Två "visslingar" hördes .</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3682,47 +3811,48 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133128748</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119403328</v>
+        <v>133094051</v>
       </c>
       <c r="B27" t="n">
-        <v>57505</v>
+        <v>58225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100134</v>
+        <v>100124</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skräntärna</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydroprogne caspia</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
@@ -3766,27 +3896,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>drog nog mot söder efter en stunds födosökande</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3810,40 +3935,45 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133094051</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134496485</v>
+        <v>119403328</v>
       </c>
       <c r="B28" t="n">
-        <v>57162</v>
+        <v>57505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100134</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skräntärna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydroprogne caspia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3851,14 +3981,10 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3898,22 +4024,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>drog nog mot söder efter en stunds födosökande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3937,13 +4068,18 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119403328</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120105932</v>
+        <v>134496485</v>
       </c>
       <c r="B29" t="n">
-        <v>57903</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3951,21 +4087,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102110</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3985,7 +4121,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4025,22 +4161,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4064,47 +4200,60 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134496485</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129145276</v>
+        <v>120105932</v>
       </c>
       <c r="B30" t="n">
-        <v>58607</v>
+        <v>57903</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102124</v>
+        <v>102110</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4144,22 +4293,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4179,59 +4328,56 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson, Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105932</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123949465</v>
+        <v>129145276</v>
       </c>
       <c r="B31" t="n">
-        <v>57981</v>
+        <v>58607</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102611</v>
+        <v>102124</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Vinterhämpling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Linaria flavirostris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4271,22 +4417,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4306,17 +4452,22 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Per-Arne Fransson, Hans Boberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129145276</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119368623</v>
+        <v>123949465</v>
       </c>
       <c r="B32" t="n">
-        <v>57144</v>
+        <v>57981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,21 +4475,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102613</v>
+        <v>102611</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4358,7 +4509,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4398,22 +4549,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4437,13 +4588,18 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123949465</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133262441</v>
+        <v>119368623</v>
       </c>
       <c r="B33" t="n">
-        <v>57165</v>
+        <v>57144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4470,30 +4626,38 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R33" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4517,22 +4681,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4547,39 +4711,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119368623</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119403883</v>
+        <v>133262441</v>
       </c>
       <c r="B34" t="n">
-        <v>58424</v>
+        <v>57165</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102624</v>
+        <v>102613</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4589,30 +4758,30 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R34" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4636,34 +4805,29 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>hördes från vassen ett par ggr.</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4671,44 +4835,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262441</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134496577</v>
+        <v>119403883</v>
       </c>
       <c r="B35" t="n">
-        <v>58061</v>
+        <v>58424</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102626</v>
+        <v>102624</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4716,19 +4885,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4768,29 +4929,34 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hördes från vassen ett par ggr.</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -4807,47 +4973,60 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119403883</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120264782</v>
+        <v>134496577</v>
       </c>
       <c r="B36" t="n">
-        <v>57094</v>
+        <v>58061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102931</v>
+        <v>102626</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4887,22 +5066,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4926,13 +5105,18 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134496577</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123949382</v>
+        <v>120264782</v>
       </c>
       <c r="B37" t="n">
-        <v>57105</v>
+        <v>57094</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,33 +5124,33 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102932</v>
+        <v>102931</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5006,22 +5190,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5045,13 +5229,18 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120264782</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133262975</v>
+        <v>123949382</v>
       </c>
       <c r="B38" t="n">
-        <v>57125</v>
+        <v>57105</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5078,26 +5267,30 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R38" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5121,22 +5314,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5151,22 +5344,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123949382</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119453310</v>
+        <v>133262975</v>
       </c>
       <c r="B39" t="n">
-        <v>57364</v>
+        <v>57125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5174,49 +5372,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102954</v>
+        <v>102932</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R39" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5240,22 +5434,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5270,22 +5464,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262975</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133263133</v>
+        <v>119453310</v>
       </c>
       <c r="B40" t="n">
-        <v>57386</v>
+        <v>57364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5317,21 +5516,25 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R40" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5355,22 +5558,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5385,22 +5588,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119453310</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133263328</v>
+        <v>133263133</v>
       </c>
       <c r="B41" t="n">
-        <v>57391</v>
+        <v>57386</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,21 +5616,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102961</v>
+        <v>102954</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5509,13 +5717,18 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263133</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123406233</v>
+        <v>133263328</v>
       </c>
       <c r="B42" t="n">
-        <v>57546</v>
+        <v>57391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5523,49 +5736,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102963</v>
+        <v>102961</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R42" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5589,22 +5798,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5619,22 +5828,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263328</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133263093</v>
+        <v>123406233</v>
       </c>
       <c r="B43" t="n">
-        <v>57568</v>
+        <v>57546</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5661,26 +5875,30 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R43" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5704,22 +5922,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5734,72 +5952,73 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406233</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132443947</v>
+        <v>133263093</v>
       </c>
       <c r="B44" t="n">
-        <v>57557</v>
+        <v>57568</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102964</v>
+        <v>102963</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R44" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5823,22 +6042,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5853,60 +6072,61 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263093</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119118339</v>
+        <v>132443947</v>
       </c>
       <c r="B45" t="n">
-        <v>57563</v>
+        <v>57557</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102966</v>
+        <v>102964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5946,22 +6166,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5985,13 +6205,18 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132443947</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133263165</v>
+        <v>119118339</v>
       </c>
       <c r="B46" t="n">
-        <v>57585</v>
+        <v>57563</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6018,26 +6243,34 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R46" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6061,22 +6294,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6091,44 +6324,49 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119118339</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123406081</v>
+        <v>133263165</v>
       </c>
       <c r="B47" t="n">
-        <v>57238</v>
+        <v>57585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102972</v>
+        <v>102966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Turkduva</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Streptopelia decaocto</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Frivaldszky, 1838)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6138,25 +6376,21 @@
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R47" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6180,27 +6414,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ensam</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6215,56 +6444,61 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263165</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126624361</v>
+        <v>123406081</v>
       </c>
       <c r="B48" t="n">
-        <v>57774</v>
+        <v>57238</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102976</v>
+        <v>102972</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Turkduva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Streptopelia decaocto</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Frivaldszky, 1838)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6304,22 +6538,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ensam</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6343,47 +6582,52 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406081</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119368994</v>
+        <v>126624361</v>
       </c>
       <c r="B49" t="n">
-        <v>58209</v>
+        <v>57774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102980</v>
+        <v>102976</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6423,22 +6667,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6462,13 +6706,18 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126624361</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133263038</v>
+        <v>119368994</v>
       </c>
       <c r="B50" t="n">
-        <v>58231</v>
+        <v>58209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6495,30 +6744,30 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R50" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6542,22 +6791,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6572,22 +6821,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119368994</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119030222</v>
+        <v>133263038</v>
       </c>
       <c r="B51" t="n">
-        <v>58541</v>
+        <v>58231</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6595,16 +6849,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6614,30 +6868,30 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R51" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6661,22 +6915,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6691,22 +6945,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263038</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133262639</v>
+        <v>119030222</v>
       </c>
       <c r="B52" t="n">
-        <v>58563</v>
+        <v>58541</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6733,26 +6992,30 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R52" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6776,22 +7039,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6806,22 +7069,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119030222</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120181415</v>
+        <v>133262639</v>
       </c>
       <c r="B53" t="n">
-        <v>58497</v>
+        <v>58563</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6829,21 +7097,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6853,25 +7121,21 @@
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R53" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6895,22 +7159,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6925,39 +7189,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262639</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125041276</v>
+        <v>120181415</v>
       </c>
       <c r="B54" t="n">
-        <v>58463</v>
+        <v>58497</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102995</v>
+        <v>102990</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6967,14 +7236,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7014,22 +7283,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7053,13 +7322,18 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120181415</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133263233</v>
+        <v>125041276</v>
       </c>
       <c r="B55" t="n">
-        <v>58485</v>
+        <v>58463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7091,21 +7365,25 @@
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R55" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7129,22 +7407,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7159,72 +7437,73 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041276</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123949544</v>
+        <v>133263233</v>
       </c>
       <c r="B56" t="n">
-        <v>58393</v>
+        <v>58485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102999</v>
+        <v>102995</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R56" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7248,22 +7527,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7278,22 +7557,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263233</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120105993</v>
+        <v>123949544</v>
       </c>
       <c r="B57" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7301,33 +7585,33 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7367,22 +7651,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7406,13 +7690,18 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123949544</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118967242</v>
+        <v>120105993</v>
       </c>
       <c r="B58" t="n">
-        <v>58179</v>
+        <v>58388</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7420,33 +7709,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103006</v>
+        <v>103001</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7486,22 +7775,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7525,10 +7814,15 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120105993</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129410071</v>
+        <v>118967242</v>
       </c>
       <c r="B59" t="n">
         <v>58179</v>
@@ -7556,28 +7850,32 @@
           <t>(Hermann, 1804)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryd, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>453198</v>
+        <v>453205</v>
       </c>
       <c r="R59" t="n">
-        <v>6377053</v>
+        <v>6377057</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7601,22 +7899,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7631,51 +7929,52 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967242</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125041320</v>
+        <v>129410071</v>
       </c>
       <c r="B60" t="n">
-        <v>58286</v>
+        <v>58179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103008</v>
+        <v>103006</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hermann, 1804)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
@@ -7686,17 +7985,17 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>453205</v>
+        <v>453198</v>
       </c>
       <c r="R60" t="n">
-        <v>6377057</v>
+        <v>6377053</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7720,22 +8019,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7750,22 +8049,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129410071</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119369191</v>
+        <v>125041320</v>
       </c>
       <c r="B61" t="n">
-        <v>58327</v>
+        <v>58286</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7773,16 +8077,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7792,14 +8096,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7839,22 +8143,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7878,13 +8182,18 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041320</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133011150</v>
+        <v>119369191</v>
       </c>
       <c r="B62" t="n">
-        <v>58461</v>
+        <v>58327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7892,33 +8201,33 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7958,22 +8267,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7997,47 +8306,52 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119369191</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118967260</v>
+        <v>133011150</v>
       </c>
       <c r="B63" t="n">
-        <v>58112</v>
+        <v>58461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8077,22 +8391,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8116,13 +8430,18 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133011150</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119369165</v>
+        <v>118967260</v>
       </c>
       <c r="B64" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8130,26 +8449,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -8196,22 +8515,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8235,13 +8554,18 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967260</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133262933</v>
+        <v>119369165</v>
       </c>
       <c r="B65" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8268,30 +8592,30 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R65" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8315,22 +8639,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8345,54 +8669,63 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119369165</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133262611</v>
+        <v>133262933</v>
       </c>
       <c r="B66" t="n">
-        <v>58104</v>
+        <v>58136</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103035</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8469,30 +8802,35 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262933</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123406104</v>
+        <v>133262611</v>
       </c>
       <c r="B67" t="n">
-        <v>58353</v>
+        <v>58104</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8502,30 +8840,26 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R67" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8549,22 +8883,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8579,39 +8913,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262611</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132443990</v>
+        <v>123406104</v>
       </c>
       <c r="B68" t="n">
-        <v>58596</v>
+        <v>58353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103041</v>
+        <v>103037</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8621,7 +8960,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -8668,22 +9007,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8707,47 +9046,52 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123406104</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120060261</v>
+        <v>132443990</v>
       </c>
       <c r="B69" t="n">
-        <v>58602</v>
+        <v>58596</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103042</v>
+        <v>103041</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8787,22 +9131,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8826,30 +9170,35 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132443990</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119369236</v>
+        <v>120060261</v>
       </c>
       <c r="B70" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8859,14 +9208,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -8906,22 +9255,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8945,13 +9294,18 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120060261</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118967313</v>
+        <v>119369236</v>
       </c>
       <c r="B71" t="n">
-        <v>58649</v>
+        <v>58636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8959,16 +9313,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8985,7 +9339,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9025,22 +9379,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9064,13 +9418,18 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119369236</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133262505</v>
+        <v>118967313</v>
       </c>
       <c r="B72" t="n">
-        <v>58671</v>
+        <v>58649</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9097,30 +9456,30 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R72" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9144,22 +9503,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9174,72 +9533,77 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967313</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132059774</v>
+        <v>133262505</v>
       </c>
       <c r="B73" t="n">
-        <v>57914</v>
+        <v>58671</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103060</v>
+        <v>103057</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R73" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9263,22 +9627,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9293,56 +9657,61 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133262505</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119403340</v>
+        <v>132059774</v>
       </c>
       <c r="B74" t="n">
-        <v>57738</v>
+        <v>57914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>205497</v>
+        <v>103060</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Brun glada</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Milvus migrans</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -9382,17 +9751,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -9421,13 +9790,18 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132059774</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123949519</v>
+        <v>119403340</v>
       </c>
       <c r="B75" t="n">
-        <v>57572</v>
+        <v>57738</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9435,16 +9809,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>205660</v>
+        <v>205497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Ägretthäger</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Ardea alba</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9454,18 +9828,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -9505,27 +9875,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>med 6 Fiskmåsar</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9549,30 +9914,35 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119403340</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118967185</v>
+        <v>123949519</v>
       </c>
       <c r="B76" t="n">
-        <v>58085</v>
+        <v>57572</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>205976</v>
+        <v>205660</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9582,14 +9952,18 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -9629,22 +10003,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>med 6 Fiskmåsar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9668,13 +10047,18 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123949519</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>78986241</v>
+        <v>118967185</v>
       </c>
       <c r="B77" t="n">
-        <v>56884</v>
+        <v>58085</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9682,34 +10066,33 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>208255</v>
+        <v>205976</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -9749,22 +10132,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9773,7 +10156,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9789,13 +10171,18 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967185</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>86131648</v>
+        <v>78986241</v>
       </c>
       <c r="B78" t="n">
-        <v>45298</v>
+        <v>56884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9803,21 +10190,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>208306</v>
+        <v>208255</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9826,11 +10213,7 @@
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
@@ -9840,17 +10223,17 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>453186</v>
+        <v>453205</v>
       </c>
       <c r="R78" t="n">
-        <v>6377118</v>
+        <v>6377057</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9874,22 +10257,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2019-07-19</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9905,17 +10288,232 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78986241</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>86131648</v>
+      </c>
+      <c r="B79" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>453186</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6377118</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
           <t>Bo Andersson</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
+      <c r="AX79" t="inlineStr">
         <is>
           <t>Bo Andersson</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86131648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -2311,7 +2311,7 @@
         <v>135507212</v>
       </c>
       <c r="B15" t="n">
-        <v>57366</v>
+        <v>57371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135560489</v>
       </c>
       <c r="B25" t="n">
-        <v>57436</v>
+        <v>57441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ77"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,27 +2308,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99972724</v>
+        <v>135507212</v>
       </c>
       <c r="B15" t="n">
-        <v>56766</v>
+        <v>57371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100077</v>
+        <v>100075</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Myrspov</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Limosa lapponica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2338,14 +2338,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2385,22 +2385,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-04-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2426,16 +2426,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99972724</t>
+          <t>https://artportalen.se/Sighting/135507212</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123405827</v>
+        <v>99972724</v>
       </c>
       <c r="B16" t="n">
-        <v>57049</v>
+        <v>56766</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,16 +2443,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100079</v>
+        <v>100077</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salskrake</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mergellus albellus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2509,27 +2509,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 hanar och 1 hona</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2555,16 +2550,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123405827</t>
+          <t>https://artportalen.se/Sighting/99972724</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119030176</v>
+        <v>123405827</v>
       </c>
       <c r="B17" t="n">
-        <v>57890</v>
+        <v>57049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,16 +2567,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100082</v>
+        <v>100079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Salskrake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Mergellus albellus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2591,18 +2586,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2642,27 +2633,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>över Målen</t>
+          <t>2 hanar och 1 hona</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2688,16 +2679,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119030176</t>
+          <t>https://artportalen.se/Sighting/123405827</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133263241</v>
+        <v>119030176</v>
       </c>
       <c r="B18" t="n">
-        <v>57912</v>
+        <v>57890</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,26 +2715,34 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R18" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,22 +2766,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>över Målen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2797,44 +2801,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133263241</t>
+          <t>https://artportalen.se/Sighting/119030176</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119813682</v>
+        <v>133263241</v>
       </c>
       <c r="B19" t="n">
-        <v>58067</v>
+        <v>57912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100090</v>
+        <v>100082</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nucifraga caryocatactes</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2844,30 +2848,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R19" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2891,22 +2891,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2921,44 +2921,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119813682</t>
+          <t>https://artportalen.se/Sighting/133263241</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123949501</v>
+        <v>119813682</v>
       </c>
       <c r="B20" t="n">
-        <v>57340</v>
+        <v>58067</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100091</v>
+        <v>100090</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2968,14 +2968,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3015,22 +3015,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3056,33 +3056,33 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123949501</t>
+          <t>https://artportalen.se/Sighting/119813682</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119030171</v>
+        <v>123949501</v>
       </c>
       <c r="B21" t="n">
-        <v>57825</v>
+        <v>57340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100096</v>
+        <v>100091</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3092,14 +3092,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3139,22 +3139,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3180,16 +3180,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119030171</t>
+          <t>https://artportalen.se/Sighting/123949501</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133262669</v>
+        <v>119030171</v>
       </c>
       <c r="B22" t="n">
-        <v>57847</v>
+        <v>57825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3221,21 +3221,25 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R22" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3259,22 +3263,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,44 +3293,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262669</t>
+          <t>https://artportalen.se/Sighting/119030171</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119118353</v>
+        <v>133262669</v>
       </c>
       <c r="B23" t="n">
-        <v>57838</v>
+        <v>57847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100100</v>
+        <v>100096</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3339,35 +3343,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R23" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3391,22 +3383,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3421,49 +3413,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119118353</t>
+          <t>https://artportalen.se/Sighting/133262669</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133128748</v>
+        <v>119118353</v>
       </c>
       <c r="B24" t="n">
-        <v>57291</v>
+        <v>57838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100116</v>
+        <v>100100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Småfläckig sumphöna</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porzana porzana</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3471,11 +3463,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3515,27 +3515,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Två "visslingar" hördes .</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3561,33 +3556,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133128748</t>
+          <t>https://artportalen.se/Sighting/119118353</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133094051</v>
+        <v>135560489</v>
       </c>
       <c r="B25" t="n">
-        <v>58225</v>
+        <v>57441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100124</v>
+        <v>100103</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backsvala</t>
+          <t>Brushane</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Riparia riparia</t>
+          <t>Calidris pugnax</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3597,14 +3592,18 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3644,22 +3643,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3685,54 +3684,50 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133094051</t>
+          <t>https://artportalen.se/Sighting/135560489</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119403328</v>
+        <v>133128748</v>
       </c>
       <c r="B26" t="n">
-        <v>57505</v>
+        <v>57291</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100134</v>
+        <v>100116</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skräntärna</t>
+          <t>Småfläckig sumphöna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydroprogne caspia</t>
+          <t>Porzana porzana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3772,27 +3767,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>drog nog mot söder efter en stunds födosökande</t>
+          <t>Två "visslingar" hördes .</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3818,38 +3813,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119403328</t>
+          <t>https://artportalen.se/Sighting/133128748</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134496485</v>
+        <v>133094051</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>58225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100124</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Backsvala</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Riparia riparia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3857,19 +3852,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3909,22 +3896,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3950,43 +3937,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134496485</t>
+          <t>https://artportalen.se/Sighting/133094051</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120105932</v>
+        <v>119403328</v>
       </c>
       <c r="B28" t="n">
-        <v>57903</v>
+        <v>57505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102110</v>
+        <v>100134</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Skräntärna</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Hydroprogne caspia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Pallas, 1770)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3994,14 +3981,10 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4041,22 +4024,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>drog nog mot söder efter en stunds födosökande</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4082,50 +4070,58 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120105932</t>
+          <t>https://artportalen.se/Sighting/119403328</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129145276</v>
+        <v>134496485</v>
       </c>
       <c r="B29" t="n">
-        <v>58607</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102124</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>sträckande SV</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4165,22 +4161,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4200,22 +4196,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson, Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129145276</t>
+          <t>https://artportalen.se/Sighting/134496485</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123949465</v>
+        <v>120105932</v>
       </c>
       <c r="B30" t="n">
-        <v>57981</v>
+        <v>57903</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4223,21 +4219,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102611</v>
+        <v>102110</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4257,7 +4253,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4297,22 +4293,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4338,33 +4334,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123949465</t>
+          <t>https://artportalen.se/Sighting/120105932</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119368623</v>
+        <v>129145276</v>
       </c>
       <c r="B31" t="n">
-        <v>57144</v>
+        <v>58607</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102613</v>
+        <v>102124</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vinterhämpling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Linaria flavirostris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4374,22 +4370,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande SV</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4429,22 +4417,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4464,22 +4452,22 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Per-Arne Fransson, Hans Boberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119368623</t>
+          <t>https://artportalen.se/Sighting/129145276</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133262441</v>
+        <v>123949465</v>
       </c>
       <c r="B32" t="n">
-        <v>57165</v>
+        <v>57981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4487,49 +4475,57 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102613</v>
+        <v>102611</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R32" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4553,22 +4549,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4583,44 +4579,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262441</t>
+          <t>https://artportalen.se/Sighting/123949465</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119403883</v>
+        <v>119368623</v>
       </c>
       <c r="B33" t="n">
-        <v>58424</v>
+        <v>57144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102624</v>
+        <v>102613</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåhake</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Luscinia svecica</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4633,11 +4629,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4677,34 +4681,29 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hördes från vassen ett par ggr.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4723,16 +4722,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119403883</t>
+          <t>https://artportalen.se/Sighting/119368623</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134496577</v>
+        <v>133262441</v>
       </c>
       <c r="B34" t="n">
-        <v>58061</v>
+        <v>57165</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4740,57 +4739,49 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102626</v>
+        <v>102613</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R34" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4814,22 +4805,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4844,27 +4835,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134496577</t>
+          <t>https://artportalen.se/Sighting/133262441</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120264782</v>
+        <v>119403883</v>
       </c>
       <c r="B35" t="n">
-        <v>57094</v>
+        <v>58424</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4872,16 +4863,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102931</v>
+        <v>102624</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Blåhake</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Luscinia svecica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4891,14 +4882,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4938,29 +4929,34 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>hördes från vassen ett par ggr.</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -4979,33 +4975,33 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120264782</t>
+          <t>https://artportalen.se/Sighting/119403883</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123949382</v>
+        <v>134496577</v>
       </c>
       <c r="B36" t="n">
-        <v>57105</v>
+        <v>58061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102932</v>
+        <v>102626</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5018,11 +5014,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5062,22 +5066,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5103,16 +5107,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123949382</t>
+          <t>https://artportalen.se/Sighting/134496577</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133262975</v>
+        <v>120264782</v>
       </c>
       <c r="B37" t="n">
-        <v>57125</v>
+        <v>57094</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5120,45 +5124,49 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102932</v>
+        <v>102931</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Bläsand</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Mareca penelope</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R37" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5182,22 +5190,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5212,27 +5220,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262975</t>
+          <t>https://artportalen.se/Sighting/120264782</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119453310</v>
+        <v>123949382</v>
       </c>
       <c r="B38" t="n">
-        <v>57364</v>
+        <v>57105</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5240,21 +5248,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102954</v>
+        <v>102932</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5266,7 +5274,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5306,22 +5314,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5347,16 +5355,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119453310</t>
+          <t>https://artportalen.se/Sighting/123949382</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133263133</v>
+        <v>133262975</v>
       </c>
       <c r="B39" t="n">
-        <v>57386</v>
+        <v>57125</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5364,26 +5372,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102954</v>
+        <v>102932</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -5467,16 +5475,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133263133</t>
+          <t>https://artportalen.se/Sighting/133262975</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133263328</v>
+        <v>119453310</v>
       </c>
       <c r="B40" t="n">
-        <v>57391</v>
+        <v>57364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5484,21 +5492,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102961</v>
+        <v>102954</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5508,21 +5516,25 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R40" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5546,22 +5558,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-31</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5576,27 +5588,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133263328</t>
+          <t>https://artportalen.se/Sighting/119453310</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123406233</v>
+        <v>133263133</v>
       </c>
       <c r="B41" t="n">
-        <v>57546</v>
+        <v>57386</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5604,16 +5616,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102963</v>
+        <v>102954</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5623,30 +5635,26 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R41" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5670,22 +5678,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5700,27 +5708,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123406233</t>
+          <t>https://artportalen.se/Sighting/133263133</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133263093</v>
+        <v>133263328</v>
       </c>
       <c r="B42" t="n">
-        <v>57568</v>
+        <v>57391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5728,26 +5736,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102963</v>
+        <v>102961</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5831,38 +5839,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133263093</t>
+          <t>https://artportalen.se/Sighting/133263328</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132443947</v>
+        <v>123406233</v>
       </c>
       <c r="B43" t="n">
-        <v>57557</v>
+        <v>57546</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102964</v>
+        <v>102963</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5914,22 +5922,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5955,70 +5963,62 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132443947</t>
+          <t>https://artportalen.se/Sighting/123406233</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119118339</v>
+        <v>133263093</v>
       </c>
       <c r="B44" t="n">
-        <v>57563</v>
+        <v>57568</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102966</v>
+        <v>102963</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R44" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6042,22 +6042,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6072,73 +6072,77 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119118339</t>
+          <t>https://artportalen.se/Sighting/133263093</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133263165</v>
+        <v>132443947</v>
       </c>
       <c r="B45" t="n">
-        <v>57585</v>
+        <v>57557</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102966</v>
+        <v>102964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Fiskmås</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Larus canus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R45" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6162,22 +6166,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6192,61 +6196,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133263165</t>
+          <t>https://artportalen.se/Sighting/132443947</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123406081</v>
+        <v>119118339</v>
       </c>
       <c r="B46" t="n">
-        <v>57238</v>
+        <v>57563</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102972</v>
+        <v>102966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Turkduva</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Streptopelia decaocto</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Frivaldszky, 1838)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6286,27 +6294,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ensam</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6332,16 +6335,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123406081</t>
+          <t>https://artportalen.se/Sighting/119118339</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126624361</v>
+        <v>133263165</v>
       </c>
       <c r="B47" t="n">
-        <v>57774</v>
+        <v>57585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6349,49 +6352,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102976</v>
+        <v>102966</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R47" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6415,22 +6414,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6445,27 +6444,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126624361</t>
+          <t>https://artportalen.se/Sighting/133263165</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119368994</v>
+        <v>123406081</v>
       </c>
       <c r="B48" t="n">
-        <v>58209</v>
+        <v>57238</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6473,33 +6472,33 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102980</v>
+        <v>102972</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Turkduva</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Streptopelia decaocto</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Frivaldszky, 1838)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6539,7 +6538,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6549,12 +6548,17 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ensam</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6580,66 +6584,66 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119368994</t>
+          <t>https://artportalen.se/Sighting/123406081</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133263038</v>
+        <v>126624361</v>
       </c>
       <c r="B49" t="n">
-        <v>58231</v>
+        <v>57774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102980</v>
+        <v>102976</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R49" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6663,22 +6667,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6693,27 +6697,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133263038</t>
+          <t>https://artportalen.se/Sighting/126624361</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119030222</v>
+        <v>119368994</v>
       </c>
       <c r="B50" t="n">
-        <v>58541</v>
+        <v>58209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6721,16 +6725,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6740,7 +6744,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6787,22 +6791,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6828,16 +6832,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119030222</t>
+          <t>https://artportalen.se/Sighting/119368994</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133262639</v>
+        <v>133263038</v>
       </c>
       <c r="B51" t="n">
-        <v>58563</v>
+        <v>58231</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6845,16 +6849,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6864,12 +6868,16 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6948,16 +6956,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262639</t>
+          <t>https://artportalen.se/Sighting/133263038</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120181415</v>
+        <v>119030222</v>
       </c>
       <c r="B52" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6965,33 +6973,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7031,22 +7039,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7072,66 +7080,62 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120181415</t>
+          <t>https://artportalen.se/Sighting/119030222</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125041276</v>
+        <v>133262639</v>
       </c>
       <c r="B53" t="n">
-        <v>58463</v>
+        <v>58563</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102995</v>
+        <v>102987</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R53" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7155,22 +7159,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7185,44 +7189,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125041276</t>
+          <t>https://artportalen.se/Sighting/133262639</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133263233</v>
+        <v>120181415</v>
       </c>
       <c r="B54" t="n">
-        <v>58485</v>
+        <v>58497</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102995</v>
+        <v>102990</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -7232,26 +7236,30 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R54" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7275,22 +7283,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7305,61 +7313,61 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133263233</t>
+          <t>https://artportalen.se/Sighting/120181415</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123949544</v>
+        <v>125041276</v>
       </c>
       <c r="B55" t="n">
-        <v>58393</v>
+        <v>58463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102999</v>
+        <v>102995</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7399,22 +7407,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7440,66 +7448,62 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123949544</t>
+          <t>https://artportalen.se/Sighting/125041276</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120105993</v>
+        <v>133263233</v>
       </c>
       <c r="B56" t="n">
-        <v>58388</v>
+        <v>58485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103001</v>
+        <v>102995</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R56" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7523,22 +7527,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7553,27 +7557,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120105993</t>
+          <t>https://artportalen.se/Sighting/133263233</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118967242</v>
+        <v>123949544</v>
       </c>
       <c r="B57" t="n">
-        <v>58179</v>
+        <v>58393</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7581,33 +7585,33 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103006</v>
+        <v>102999</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7647,22 +7651,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7688,16 +7692,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967242</t>
+          <t>https://artportalen.se/Sighting/123949544</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129410071</v>
+        <v>120105993</v>
       </c>
       <c r="B58" t="n">
-        <v>58179</v>
+        <v>58388</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7705,45 +7709,49 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103006</v>
+        <v>103001</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryd, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>453198</v>
+        <v>453205</v>
       </c>
       <c r="R58" t="n">
-        <v>6377053</v>
+        <v>6377057</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7767,22 +7775,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7797,61 +7805,61 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Gustav Lundqvist</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129410071</t>
+          <t>https://artportalen.se/Sighting/120105993</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125041320</v>
+        <v>118967242</v>
       </c>
       <c r="B59" t="n">
-        <v>58286</v>
+        <v>58179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103008</v>
+        <v>103006</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hermann, 1804)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7891,22 +7899,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7932,66 +7940,62 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125041320</t>
+          <t>https://artportalen.se/Sighting/118967242</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119369191</v>
+        <v>129410071</v>
       </c>
       <c r="B60" t="n">
-        <v>58327</v>
+        <v>58179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>103006</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hermann, 1804)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>453205</v>
+        <v>453198</v>
       </c>
       <c r="R60" t="n">
-        <v>6377057</v>
+        <v>6377053</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8015,22 +8019,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8045,27 +8049,27 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Gustav Lundqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119369191</t>
+          <t>https://artportalen.se/Sighting/129410071</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133011150</v>
+        <v>125041320</v>
       </c>
       <c r="B61" t="n">
-        <v>58461</v>
+        <v>58286</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8073,21 +8077,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103018</v>
+        <v>103008</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8139,22 +8143,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8180,33 +8184,33 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133011150</t>
+          <t>https://artportalen.se/Sighting/125041320</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118967260</v>
+        <v>119369191</v>
       </c>
       <c r="B62" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8263,22 +8267,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8304,50 +8308,50 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967260</t>
+          <t>https://artportalen.se/Sighting/119369191</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119369165</v>
+        <v>133011150</v>
       </c>
       <c r="B63" t="n">
-        <v>58114</v>
+        <v>58461</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8387,22 +8391,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8428,16 +8432,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119369165</t>
+          <t>https://artportalen.se/Sighting/133011150</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133262933</v>
+        <v>118967260</v>
       </c>
       <c r="B64" t="n">
-        <v>58136</v>
+        <v>58112</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8445,49 +8449,49 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R64" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8511,22 +8515,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8541,73 +8545,77 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262933</t>
+          <t>https://artportalen.se/Sighting/118967260</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133262611</v>
+        <v>119369165</v>
       </c>
       <c r="B65" t="n">
-        <v>58104</v>
+        <v>58114</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103035</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R65" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8631,22 +8639,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8661,77 +8669,77 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262611</t>
+          <t>https://artportalen.se/Sighting/119369165</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123406104</v>
+        <v>133262933</v>
       </c>
       <c r="B66" t="n">
-        <v>58353</v>
+        <v>58136</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103037</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R66" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8755,22 +8763,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8785,27 +8793,27 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123406104</t>
+          <t>https://artportalen.se/Sighting/133262933</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132443990</v>
+        <v>133262611</v>
       </c>
       <c r="B67" t="n">
-        <v>58596</v>
+        <v>58104</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8813,16 +8821,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103041</v>
+        <v>103035</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8832,30 +8840,26 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R67" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8879,22 +8883,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8909,27 +8913,27 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132443990</t>
+          <t>https://artportalen.se/Sighting/133262611</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120060261</v>
+        <v>123406104</v>
       </c>
       <c r="B68" t="n">
-        <v>58602</v>
+        <v>58353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8937,33 +8941,33 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -9003,22 +9007,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9044,16 +9048,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120060261</t>
+          <t>https://artportalen.se/Sighting/123406104</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119369236</v>
+        <v>132443990</v>
       </c>
       <c r="B69" t="n">
-        <v>58636</v>
+        <v>58596</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9061,33 +9065,33 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>103041</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -9127,22 +9131,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9168,33 +9172,33 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119369236</t>
+          <t>https://artportalen.se/Sighting/132443990</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118967313</v>
+        <v>120060261</v>
       </c>
       <c r="B70" t="n">
-        <v>58649</v>
+        <v>58602</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103057</v>
+        <v>103042</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9204,14 +9208,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9251,22 +9255,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9292,16 +9296,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967313</t>
+          <t>https://artportalen.se/Sighting/120060261</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133262505</v>
+        <v>119369236</v>
       </c>
       <c r="B71" t="n">
-        <v>58671</v>
+        <v>58636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9309,16 +9313,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103057</v>
+        <v>103044</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9328,30 +9332,30 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>453157</v>
+        <v>453205</v>
       </c>
       <c r="R71" t="n">
-        <v>6377067</v>
+        <v>6377057</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9375,22 +9379,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9405,61 +9409,61 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133262505</t>
+          <t>https://artportalen.se/Sighting/119369236</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132059774</v>
+        <v>118967313</v>
       </c>
       <c r="B72" t="n">
-        <v>57914</v>
+        <v>58649</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103060</v>
+        <v>103057</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>sträckande N</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -9499,22 +9503,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9540,66 +9544,66 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132059774</t>
+          <t>https://artportalen.se/Sighting/118967313</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119403340</v>
+        <v>133262505</v>
       </c>
       <c r="B73" t="n">
-        <v>57738</v>
+        <v>58671</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>205497</v>
+        <v>103057</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+          <t>Sandsjön, Vaggeryds k:n, Sm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>453205</v>
+        <v>453157</v>
       </c>
       <c r="R73" t="n">
-        <v>6377057</v>
+        <v>6377067</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9623,22 +9627,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>05:50</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9653,49 +9657,49 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Per-Arne Fransson</t>
+          <t>Hans Boberg, Per-Arne Fransson, Per Landin, Andreas Ljung</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119403340</t>
+          <t>https://artportalen.se/Sighting/133262505</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123949519</v>
+        <v>132059774</v>
       </c>
       <c r="B74" t="n">
-        <v>57572</v>
+        <v>57914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>205660</v>
+        <v>103060</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Silltrut</t>
+          <t>Brun glada</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Larus fuscus</t>
+          <t>Milvus migrans</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9703,11 +9707,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
@@ -9751,27 +9751,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>med 6 Fiskmåsar</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9797,33 +9792,33 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123949519</t>
+          <t>https://artportalen.se/Sighting/132059774</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118967185</v>
+        <v>119403340</v>
       </c>
       <c r="B75" t="n">
-        <v>58085</v>
+        <v>57738</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>205976</v>
+        <v>205497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Ägretthäger</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Ardea alba</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9833,14 +9828,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -9880,22 +9875,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9921,38 +9916,38 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118967185</t>
+          <t>https://artportalen.se/Sighting/119403340</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>78986241</v>
+        <v>123949519</v>
       </c>
       <c r="B76" t="n">
-        <v>56884</v>
+        <v>57572</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>208255</v>
+        <v>205660</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Silltrut</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Larus fuscus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9960,12 +9955,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>sträckande N</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -10005,22 +10003,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2019-07-19</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>med 6 Fiskmåsar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10029,7 +10032,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10047,16 +10049,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78986241</t>
+          <t>https://artportalen.se/Sighting/123949519</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>86131648</v>
+        <v>118967185</v>
       </c>
       <c r="B77" t="n">
-        <v>45298</v>
+        <v>58085</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,54 +10066,49 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>208306</v>
+        <v>205976</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bred kärrtrollslända</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Leucorrhinia caudalis</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Charpentier, 1840)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>453186</v>
+        <v>453205</v>
       </c>
       <c r="R77" t="n">
-        <v>6377118</v>
+        <v>6377057</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10135,22 +10132,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10159,23 +10156,278 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo Andersson</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo Andersson</t>
+          <t>Per-Arne Fransson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118967185</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>78986241</v>
+      </c>
+      <c r="B78" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tornet,Sandsjön,Vaggeryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>453205</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6377057</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2019-07-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2019-07-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Per-Arne Fransson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78986241</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>86131648</v>
+      </c>
+      <c r="B79" t="n">
+        <v>45298</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>208306</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Bred kärrtrollslända</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Leucorrhinia caudalis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Charpentier, 1840)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>tornet, Sandsjön, Vaggeryds k:n, Sm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>453186</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6377118</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Byarum</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bo Andersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bo Andersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/86131648</t>
         </is>
@@ -10259,6 +10511,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22860-2026 artfynd.xlsx
+++ b/artfynd/A 22860-2026 artfynd.xlsx
@@ -2311,7 +2311,7 @@
         <v>135507212</v>
       </c>
       <c r="B15" t="n">
-        <v>57371</v>
+        <v>57373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135560489</v>
       </c>
       <c r="B25" t="n">
-        <v>57441</v>
+        <v>57443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
